--- a/output7/【河洛文讀注音-閩拼調符】《管仲論》.xlsx
+++ b/output7/【河洛文讀注音-閩拼調符】《管仲論》.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\Piau-Im\output7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{588E2032-F257-421F-A1E2-ECDC80C94F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4AA9CE86-6A77-4235-AADB-B1AA6E351108}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="16440" windowHeight="28320" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
+    <workbookView xWindow="1410" yWindow="1545" windowWidth="33030" windowHeight="11295" activeTab="4" xr2:uid="{25A76161-EFED-4AC8-8EAA-A42737AE1909}"/>
   </bookViews>
   <sheets>
     <sheet name="缺字表" sheetId="141" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3276" uniqueCount="1101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3274" uniqueCount="1102">
   <si>
     <t>Key</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -244,10 +244,6 @@
   </si>
   <si>
     <t>(13, 8)</t>
-  </si>
-  <si>
-    <t>知否？知否？.png</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>zai1</t>
@@ -1149,6 +1145,9 @@
     <t>iu5</t>
   </si>
   <si>
+    <t>yú</t>
+  </si>
+  <si>
     <t>khi2</t>
   </si>
   <si>
@@ -3782,6 +3781,10 @@
   </si>
   <si>
     <t>suē</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>kuan-tiong-lun.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3789,7 +3792,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="37">
+  <fonts count="38">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -4045,6 +4048,12 @@
       <name val="Cascadia Code"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -4149,7 +4158,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4319,6 +4328,9 @@
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -4731,7 +4743,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7836F8C8-8FB2-4A4B-A493-5D76EA08E51E}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -4746,20 +4758,6 @@
       </c>
       <c r="D1" t="s">
         <v>697</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
-        <v>264</v>
-      </c>
-      <c r="B2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>637</v>
       </c>
     </row>
   </sheetData>
@@ -4789,10 +4787,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C2" t="s">
         <v>24</v>
@@ -4803,10 +4801,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C3" t="s">
         <v>24</v>
@@ -4817,10 +4815,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C4" t="s">
         <v>24</v>
@@ -4831,7 +4829,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B5" t="s">
         <v>702</v>
@@ -4845,21 +4843,21 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C6" t="s">
         <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B7" t="s">
         <v>46</v>
@@ -4868,29 +4866,29 @@
         <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C8" t="s">
         <v>24</v>
       </c>
       <c r="D8" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C9" t="s">
         <v>24</v>
@@ -4901,10 +4899,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C10" t="s">
         <v>24</v>
@@ -4915,10 +4913,10 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B11" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C11" t="s">
         <v>24</v>
@@ -4929,7 +4927,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B12" t="s">
         <v>715</v>
@@ -4943,10 +4941,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B13" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C13" t="s">
         <v>24</v>
@@ -4957,10 +4955,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C14" t="s">
         <v>24</v>
@@ -4971,10 +4969,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B15" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C15" t="s">
         <v>24</v>
@@ -4985,10 +4983,10 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B16" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C16" t="s">
         <v>24</v>
@@ -4999,10 +4997,10 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B17" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C17" t="s">
         <v>24</v>
@@ -5013,10 +5011,10 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B18" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C18" t="s">
         <v>24</v>
@@ -5027,24 +5025,24 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B19" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C19" t="s">
         <v>24</v>
       </c>
       <c r="D19" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B20" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C20" t="s">
         <v>24</v>
@@ -5055,7 +5053,7 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B21" t="s">
         <v>590</v>
@@ -5069,10 +5067,10 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B22" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C22" t="s">
         <v>24</v>
@@ -5083,7 +5081,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B23" t="s">
         <v>732</v>
@@ -5097,10 +5095,10 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B24" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C24" t="s">
         <v>24</v>
@@ -5111,10 +5109,10 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B25" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C25" t="s">
         <v>24</v>
@@ -5125,10 +5123,10 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B26" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C26" t="s">
         <v>24</v>
@@ -5139,10 +5137,10 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B27" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C27" t="s">
         <v>24</v>
@@ -5153,21 +5151,21 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B28" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C28" t="s">
         <v>24</v>
       </c>
       <c r="D28" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B29" t="s">
         <v>741</v>
@@ -5176,7 +5174,7 @@
         <v>24</v>
       </c>
       <c r="D29" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -5195,10 +5193,10 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B31" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C31" t="s">
         <v>24</v>
@@ -5209,10 +5207,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B32" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C32" t="s">
         <v>24</v>
@@ -5223,10 +5221,10 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B33" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C33" t="s">
         <v>24</v>
@@ -5237,7 +5235,7 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B34" t="s">
         <v>750</v>
@@ -5251,10 +5249,10 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B35" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C35" t="s">
         <v>24</v>
@@ -5265,10 +5263,10 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B36" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C36" t="s">
         <v>24</v>
@@ -5279,10 +5277,10 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B37" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C37" t="s">
         <v>24</v>
@@ -5293,10 +5291,10 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B38" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C38" t="s">
         <v>24</v>
@@ -5307,10 +5305,10 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B39" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C39" t="s">
         <v>24</v>
@@ -5321,10 +5319,10 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B40" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C40" t="s">
         <v>24</v>
@@ -5335,7 +5333,7 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B41" t="s">
         <v>44</v>
@@ -5349,10 +5347,10 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B42" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C42" t="s">
         <v>24</v>
@@ -5363,7 +5361,7 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B43" t="s">
         <v>423</v>
@@ -5377,10 +5375,10 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B44" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C44" t="s">
         <v>24</v>
@@ -5391,10 +5389,10 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B45" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C45" t="s">
         <v>24</v>
@@ -5405,10 +5403,10 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B46" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C46" t="s">
         <v>24</v>
@@ -5419,38 +5417,38 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B47" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C47" t="s">
         <v>24</v>
       </c>
       <c r="D47" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B48" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C48" t="s">
         <v>24</v>
       </c>
       <c r="D48" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B49" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C49" t="s">
         <v>24</v>
@@ -5461,35 +5459,35 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B50" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C50" t="s">
         <v>24</v>
       </c>
       <c r="D50" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B51" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C51" t="s">
         <v>24</v>
       </c>
       <c r="D51" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B52" t="s">
         <v>783</v>
@@ -5498,43 +5496,43 @@
         <v>24</v>
       </c>
       <c r="D52" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B53" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C53" t="s">
         <v>24</v>
       </c>
       <c r="D53" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B54" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C54" t="s">
         <v>24</v>
       </c>
       <c r="D54" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B55" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C55" t="s">
         <v>24</v>
@@ -5545,38 +5543,38 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B56" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C56" t="s">
         <v>24</v>
       </c>
       <c r="D56" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B57" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C57" t="s">
         <v>24</v>
       </c>
       <c r="D57" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B58" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C58" t="s">
         <v>24</v>
@@ -5587,24 +5585,24 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B59" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C59" t="s">
         <v>24</v>
       </c>
       <c r="D59" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B60" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C60" t="s">
         <v>24</v>
@@ -5615,10 +5613,10 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B61" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C61" t="s">
         <v>24</v>
@@ -5629,10 +5627,10 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B62" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C62" t="s">
         <v>24</v>
@@ -5643,10 +5641,10 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B63" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C63" t="s">
         <v>24</v>
@@ -5657,10 +5655,10 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B64" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C64" t="s">
         <v>24</v>
@@ -5671,10 +5669,10 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B65" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C65" t="s">
         <v>24</v>
@@ -5685,10 +5683,10 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B66" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C66" t="s">
         <v>24</v>
@@ -5699,10 +5697,10 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B67" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C67" t="s">
         <v>24</v>
@@ -5713,10 +5711,10 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B68" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C68" t="s">
         <v>24</v>
@@ -5727,7 +5725,7 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B69" t="s">
         <v>353</v>
@@ -5741,7 +5739,7 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B70" t="s">
         <v>354</v>
@@ -5755,10 +5753,10 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B71" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C71" t="s">
         <v>24</v>
@@ -5769,7 +5767,7 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B72" t="s">
         <v>358</v>
@@ -5783,7 +5781,7 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B73" t="s">
         <v>359</v>
@@ -5797,7 +5795,7 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B74" t="s">
         <v>360</v>
@@ -5811,7 +5809,7 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B75" t="s">
         <v>783</v>
@@ -5825,7 +5823,7 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B76" t="s">
         <v>361</v>
@@ -5839,7 +5837,7 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B77" t="s">
         <v>362</v>
@@ -5853,7 +5851,7 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B78" t="s">
         <v>366</v>
@@ -5867,7 +5865,7 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B79" t="s">
         <v>367</v>
@@ -5881,7 +5879,7 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B80" t="s">
         <v>368</v>
@@ -5895,7 +5893,7 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B81" t="s">
         <v>833</v>
@@ -5909,7 +5907,7 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B82" t="s">
         <v>369</v>
@@ -5923,7 +5921,7 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B83" t="s">
         <v>370</v>
@@ -5937,7 +5935,7 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B84" t="s">
         <v>371</v>
@@ -5951,7 +5949,7 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B85" t="s">
         <v>372</v>
@@ -5965,7 +5963,7 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B86" t="s">
         <v>373</v>
@@ -5979,7 +5977,7 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B87" t="s">
         <v>374</v>
@@ -5993,7 +5991,7 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B88" t="s">
         <v>359</v>
@@ -6021,7 +6019,7 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B90" t="s">
         <v>375</v>
@@ -6035,7 +6033,7 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B91" t="s">
         <v>359</v>
@@ -6049,7 +6047,7 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B92" t="s">
         <v>376</v>
@@ -6063,7 +6061,7 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B93" t="s">
         <v>852</v>
@@ -6077,10 +6075,10 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B94" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C94" t="s">
         <v>24</v>
@@ -6105,7 +6103,7 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B96" t="s">
         <v>379</v>
@@ -6119,7 +6117,7 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B97" t="s">
         <v>380</v>
@@ -6133,7 +6131,7 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B98" t="s">
         <v>381</v>
@@ -6147,7 +6145,7 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B99" t="s">
         <v>382</v>
@@ -6161,7 +6159,7 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B100" t="s">
         <v>863</v>
@@ -6175,7 +6173,7 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B101" t="s">
         <v>383</v>
@@ -6189,7 +6187,7 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B102" t="s">
         <v>384</v>
@@ -6203,7 +6201,7 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B103" t="s">
         <v>389</v>
@@ -6217,7 +6215,7 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B104" t="s">
         <v>390</v>
@@ -6231,10 +6229,10 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B105" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C105" t="s">
         <v>24</v>
@@ -6245,7 +6243,7 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B106" t="s">
         <v>395</v>
@@ -6259,7 +6257,7 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B107" t="s">
         <v>396</v>
@@ -6287,7 +6285,7 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B109" t="s">
         <v>397</v>
@@ -6315,7 +6313,7 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B111" t="s">
         <v>398</v>
@@ -6329,7 +6327,7 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B112" t="s">
         <v>402</v>
@@ -6343,7 +6341,7 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B113" t="s">
         <v>403</v>
@@ -6357,7 +6355,7 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B114" t="s">
         <v>404</v>
@@ -6371,7 +6369,7 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B115" t="s">
         <v>405</v>
@@ -6385,7 +6383,7 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B116" t="s">
         <v>406</v>
@@ -6399,7 +6397,7 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B117" t="s">
         <v>407</v>
@@ -6413,7 +6411,7 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B118" t="s">
         <v>408</v>
@@ -6427,7 +6425,7 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B119" t="s">
         <v>410</v>
@@ -6441,7 +6439,7 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B120" t="s">
         <v>411</v>
@@ -6455,7 +6453,7 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B121" t="s">
         <v>412</v>
@@ -6469,7 +6467,7 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B122" t="s">
         <v>420</v>
@@ -6483,7 +6481,7 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B123" t="s">
         <v>421</v>
@@ -6497,7 +6495,7 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B124" t="s">
         <v>422</v>
@@ -6511,7 +6509,7 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B125" t="s">
         <v>402</v>
@@ -6525,7 +6523,7 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B126" t="s">
         <v>423</v>
@@ -6539,7 +6537,7 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B127" t="s">
         <v>424</v>
@@ -6553,7 +6551,7 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B128" t="s">
         <v>428</v>
@@ -6567,7 +6565,7 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B129" t="s">
         <v>429</v>
@@ -6581,7 +6579,7 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B130" t="s">
         <v>916</v>
@@ -6595,10 +6593,10 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B131" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C131" t="s">
         <v>24</v>
@@ -6609,7 +6607,7 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B132" t="s">
         <v>402</v>
@@ -6623,10 +6621,10 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B133" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C133" t="s">
         <v>24</v>
@@ -6637,7 +6635,7 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B134" t="s">
         <v>23</v>
@@ -6651,7 +6649,7 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B135" t="s">
         <v>431</v>
@@ -6665,7 +6663,7 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B136" t="s">
         <v>432</v>
@@ -6679,7 +6677,7 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B137" t="s">
         <v>433</v>
@@ -6693,7 +6691,7 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B138" t="s">
         <v>438</v>
@@ -6707,7 +6705,7 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B139" t="s">
         <v>439</v>
@@ -6721,7 +6719,7 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B140" t="s">
         <v>440</v>
@@ -6735,7 +6733,7 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B141" t="s">
         <v>931</v>
@@ -6749,7 +6747,7 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B142" t="s">
         <v>441</v>
@@ -6763,7 +6761,7 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B143" t="s">
         <v>445</v>
@@ -6777,7 +6775,7 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B144" t="s">
         <v>47</v>
@@ -6791,7 +6789,7 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B145" t="s">
         <v>446</v>
@@ -6805,7 +6803,7 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B146" t="s">
         <v>452</v>
@@ -6819,7 +6817,7 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B147" t="s">
         <v>453</v>
@@ -6833,7 +6831,7 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B148" t="s">
         <v>456</v>
@@ -6847,7 +6845,7 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B149" t="s">
         <v>457</v>
@@ -6861,7 +6859,7 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B150" t="s">
         <v>458</v>
@@ -6875,7 +6873,7 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B151" t="s">
         <v>461</v>
@@ -6889,7 +6887,7 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B152" t="s">
         <v>462</v>
@@ -6903,10 +6901,10 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B153" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C153" t="s">
         <v>24</v>
@@ -6917,7 +6915,7 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B154" t="s">
         <v>466</v>
@@ -6931,7 +6929,7 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B155" t="s">
         <v>467</v>
@@ -6945,7 +6943,7 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B156" t="s">
         <v>468</v>
@@ -6959,7 +6957,7 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B157" t="s">
         <v>469</v>
@@ -6973,7 +6971,7 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B158" t="s">
         <v>470</v>
@@ -6987,7 +6985,7 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B159" t="s">
         <v>473</v>
@@ -7001,7 +6999,7 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B160" t="s">
         <v>474</v>
@@ -7015,7 +7013,7 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B161" t="s">
         <v>353</v>
@@ -7029,7 +7027,7 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B162" t="s">
         <v>970</v>
@@ -7043,7 +7041,7 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B163" t="s">
         <v>480</v>
@@ -7057,7 +7055,7 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B164" t="s">
         <v>481</v>
@@ -7071,7 +7069,7 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B165" t="s">
         <v>482</v>
@@ -7085,7 +7083,7 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B166" t="s">
         <v>483</v>
@@ -7099,7 +7097,7 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B167" t="s">
         <v>431</v>
@@ -7113,10 +7111,10 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B168" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C168" t="s">
         <v>24</v>
@@ -7127,7 +7125,7 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B169" t="s">
         <v>441</v>
@@ -7141,10 +7139,10 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" t="s">
+        <v>56</v>
+      </c>
+      <c r="B170" t="s">
         <v>57</v>
-      </c>
-      <c r="B170" t="s">
-        <v>58</v>
       </c>
       <c r="C170" t="s">
         <v>24</v>
@@ -7155,7 +7153,7 @@
     </row>
     <row r="171" spans="1:4">
       <c r="A171" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B171" t="s">
         <v>983</v>
@@ -7169,7 +7167,7 @@
     </row>
     <row r="172" spans="1:4">
       <c r="A172" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B172" t="s">
         <v>492</v>
@@ -7183,7 +7181,7 @@
     </row>
     <row r="173" spans="1:4">
       <c r="A173" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B173" t="s">
         <v>493</v>
@@ -7197,7 +7195,7 @@
     </row>
     <row r="174" spans="1:4">
       <c r="A174" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B174" t="s">
         <v>494</v>
@@ -7211,7 +7209,7 @@
     </row>
     <row r="175" spans="1:4">
       <c r="A175" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B175" t="s">
         <v>499</v>
@@ -7225,7 +7223,7 @@
     </row>
     <row r="176" spans="1:4">
       <c r="A176" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B176" t="s">
         <v>500</v>
@@ -7239,7 +7237,7 @@
     </row>
     <row r="177" spans="1:4">
       <c r="A177" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B177" t="s">
         <v>502</v>
@@ -7253,7 +7251,7 @@
     </row>
     <row r="178" spans="1:4">
       <c r="A178" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B178" t="s">
         <v>445</v>
@@ -7267,7 +7265,7 @@
     </row>
     <row r="179" spans="1:4">
       <c r="A179" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B179" t="s">
         <v>508</v>
@@ -7281,10 +7279,10 @@
     </row>
     <row r="180" spans="1:4">
       <c r="A180" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B180" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C180" t="s">
         <v>24</v>
@@ -7295,7 +7293,7 @@
     </row>
     <row r="181" spans="1:4">
       <c r="A181" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B181" t="s">
         <v>509</v>
@@ -7309,7 +7307,7 @@
     </row>
     <row r="182" spans="1:4">
       <c r="A182" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B182" t="s">
         <v>510</v>
@@ -7323,7 +7321,7 @@
     </row>
     <row r="183" spans="1:4">
       <c r="A183" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B183" t="s">
         <v>518</v>
@@ -7337,7 +7335,7 @@
     </row>
     <row r="184" spans="1:4">
       <c r="A184" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B184" t="s">
         <v>519</v>
@@ -7351,7 +7349,7 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B185" t="s">
         <v>520</v>
@@ -7365,10 +7363,10 @@
     </row>
     <row r="186" spans="1:4">
       <c r="A186" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B186" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C186" t="s">
         <v>24</v>
@@ -7379,7 +7377,7 @@
     </row>
     <row r="187" spans="1:4">
       <c r="A187" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B187" t="s">
         <v>521</v>
@@ -7393,7 +7391,7 @@
     </row>
     <row r="188" spans="1:4">
       <c r="A188" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B188" t="s">
         <v>525</v>
@@ -7407,7 +7405,7 @@
     </row>
     <row r="189" spans="1:4">
       <c r="A189" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B189" t="s">
         <v>526</v>
@@ -7421,7 +7419,7 @@
     </row>
     <row r="190" spans="1:4">
       <c r="A190" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B190" t="s">
         <v>527</v>
@@ -7435,10 +7433,10 @@
     </row>
     <row r="191" spans="1:4">
       <c r="A191" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B191" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C191" t="s">
         <v>24</v>
@@ -7449,7 +7447,7 @@
     </row>
     <row r="192" spans="1:4">
       <c r="A192" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B192" t="s">
         <v>531</v>
@@ -7463,7 +7461,7 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B193" t="s">
         <v>532</v>
@@ -7477,7 +7475,7 @@
     </row>
     <row r="194" spans="1:4">
       <c r="A194" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B194" t="s">
         <v>533</v>
@@ -7491,7 +7489,7 @@
     </row>
     <row r="195" spans="1:4">
       <c r="A195" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B195" t="s">
         <v>534</v>
@@ -7505,7 +7503,7 @@
     </row>
     <row r="196" spans="1:4">
       <c r="A196" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B196" t="s">
         <v>542</v>
@@ -7519,10 +7517,10 @@
     </row>
     <row r="197" spans="1:4">
       <c r="A197" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B197" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C197" t="s">
         <v>24</v>
@@ -7533,7 +7531,7 @@
     </row>
     <row r="198" spans="1:4">
       <c r="A198" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B198" t="s">
         <v>543</v>
@@ -7547,7 +7545,7 @@
     </row>
     <row r="199" spans="1:4">
       <c r="A199" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B199" t="s">
         <v>551</v>
@@ -7561,7 +7559,7 @@
     </row>
     <row r="200" spans="1:4">
       <c r="A200" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B200" t="s">
         <v>552</v>
@@ -7575,7 +7573,7 @@
     </row>
     <row r="201" spans="1:4">
       <c r="A201" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B201" t="s">
         <v>49</v>
@@ -7589,7 +7587,7 @@
     </row>
     <row r="202" spans="1:4">
       <c r="A202" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B202" t="s">
         <v>553</v>
@@ -7603,7 +7601,7 @@
     </row>
     <row r="203" spans="1:4">
       <c r="A203" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B203" t="s">
         <v>554</v>
@@ -7617,7 +7615,7 @@
     </row>
     <row r="204" spans="1:4">
       <c r="A204" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B204" t="s">
         <v>560</v>
@@ -7631,7 +7629,7 @@
     </row>
     <row r="205" spans="1:4">
       <c r="A205" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B205" t="s">
         <v>561</v>
@@ -7645,7 +7643,7 @@
     </row>
     <row r="206" spans="1:4">
       <c r="A206" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B206" t="s">
         <v>562</v>
@@ -7659,7 +7657,7 @@
     </row>
     <row r="207" spans="1:4">
       <c r="A207" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B207" t="s">
         <v>563</v>
@@ -7673,7 +7671,7 @@
     </row>
     <row r="208" spans="1:4">
       <c r="A208" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B208" t="s">
         <v>570</v>
@@ -7687,7 +7685,7 @@
     </row>
     <row r="209" spans="1:4">
       <c r="A209" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B209" t="s">
         <v>572</v>
@@ -7701,7 +7699,7 @@
     </row>
     <row r="210" spans="1:4">
       <c r="A210" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B210" t="s">
         <v>577</v>
@@ -7715,7 +7713,7 @@
     </row>
     <row r="211" spans="1:4">
       <c r="A211" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B211" t="s">
         <v>578</v>
@@ -7729,7 +7727,7 @@
     </row>
     <row r="212" spans="1:4">
       <c r="A212" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B212" t="s">
         <v>588</v>
@@ -7743,7 +7741,7 @@
     </row>
     <row r="213" spans="1:4">
       <c r="A213" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B213" t="s">
         <v>589</v>
@@ -7757,7 +7755,7 @@
     </row>
     <row r="214" spans="1:4">
       <c r="A214" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B214" t="s">
         <v>590</v>
@@ -7771,7 +7769,7 @@
     </row>
     <row r="215" spans="1:4">
       <c r="A215" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B215" t="s">
         <v>591</v>
@@ -7785,7 +7783,7 @@
     </row>
     <row r="216" spans="1:4">
       <c r="A216" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B216" t="s">
         <v>589</v>
@@ -7799,7 +7797,7 @@
     </row>
     <row r="217" spans="1:4">
       <c r="A217" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B217" t="s">
         <v>1058</v>
@@ -7813,10 +7811,10 @@
     </row>
     <row r="218" spans="1:4">
       <c r="A218" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B218" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C218" t="s">
         <v>24</v>
@@ -7841,7 +7839,7 @@
     </row>
     <row r="220" spans="1:4">
       <c r="A220" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B220" t="s">
         <v>599</v>
@@ -7855,7 +7853,7 @@
     </row>
     <row r="221" spans="1:4">
       <c r="A221" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B221" t="s">
         <v>600</v>
@@ -7869,7 +7867,7 @@
     </row>
     <row r="222" spans="1:4">
       <c r="A222" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B222" t="s">
         <v>607</v>
@@ -7883,7 +7881,7 @@
     </row>
     <row r="223" spans="1:4">
       <c r="A223" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B223" t="s">
         <v>608</v>
@@ -7897,7 +7895,7 @@
     </row>
     <row r="224" spans="1:4">
       <c r="A224" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B224" t="s">
         <v>1067</v>
@@ -7911,7 +7909,7 @@
     </row>
     <row r="225" spans="1:4">
       <c r="A225" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B225" t="s">
         <v>615</v>
@@ -7925,10 +7923,10 @@
     </row>
     <row r="226" spans="1:4">
       <c r="A226" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B226" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C226" t="s">
         <v>24</v>
@@ -7939,7 +7937,7 @@
     </row>
     <row r="227" spans="1:4">
       <c r="A227" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B227" t="s">
         <v>622</v>
@@ -7953,7 +7951,7 @@
     </row>
     <row r="228" spans="1:4">
       <c r="A228" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B228" t="s">
         <v>380</v>
@@ -7967,7 +7965,7 @@
     </row>
     <row r="229" spans="1:4">
       <c r="A229" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B229" t="s">
         <v>532</v>
@@ -7981,7 +7979,7 @@
     </row>
     <row r="230" spans="1:4">
       <c r="A230" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B230" t="s">
         <v>623</v>
@@ -7995,7 +7993,7 @@
     </row>
     <row r="231" spans="1:4">
       <c r="A231" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B231" t="s">
         <v>1074</v>
@@ -8009,7 +8007,7 @@
     </row>
     <row r="232" spans="1:4">
       <c r="A232" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B232" t="s">
         <v>543</v>
@@ -8023,7 +8021,7 @@
     </row>
     <row r="233" spans="1:4">
       <c r="A233" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B233" t="s">
         <v>521</v>
@@ -8037,7 +8035,7 @@
     </row>
     <row r="234" spans="1:4">
       <c r="A234" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B234" t="s">
         <v>624</v>
@@ -8051,7 +8049,7 @@
     </row>
     <row r="235" spans="1:4">
       <c r="A235" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B235" t="s">
         <v>625</v>
@@ -8065,7 +8063,7 @@
     </row>
     <row r="236" spans="1:4">
       <c r="A236" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B236" t="s">
         <v>638</v>
@@ -8079,7 +8077,7 @@
     </row>
     <row r="237" spans="1:4">
       <c r="A237" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B237" t="s">
         <v>639</v>
@@ -8093,7 +8091,7 @@
     </row>
     <row r="238" spans="1:4">
       <c r="A238" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B238" t="s">
         <v>49</v>
@@ -8107,7 +8105,7 @@
     </row>
     <row r="239" spans="1:4">
       <c r="A239" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B239" t="s">
         <v>645</v>
@@ -8121,7 +8119,7 @@
     </row>
     <row r="240" spans="1:4">
       <c r="A240" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B240" t="s">
         <v>646</v>
@@ -8135,7 +8133,7 @@
     </row>
     <row r="241" spans="1:4">
       <c r="A241" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B241" t="s">
         <v>500</v>
@@ -8149,7 +8147,7 @@
     </row>
     <row r="242" spans="1:4">
       <c r="A242" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B242" t="s">
         <v>647</v>
@@ -8163,7 +8161,7 @@
     </row>
     <row r="243" spans="1:4">
       <c r="A243" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B243" t="s">
         <v>659</v>
@@ -8177,7 +8175,7 @@
     </row>
     <row r="244" spans="1:4">
       <c r="A244" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B244" t="s">
         <v>660</v>
@@ -8191,7 +8189,7 @@
     </row>
     <row r="245" spans="1:4">
       <c r="A245" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B245" t="s">
         <v>667</v>
@@ -8205,7 +8203,7 @@
     </row>
     <row r="246" spans="1:4">
       <c r="A246" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B246" t="s">
         <v>668</v>
@@ -8219,7 +8217,7 @@
     </row>
     <row r="247" spans="1:4">
       <c r="A247" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B247" t="s">
         <v>669</v>
@@ -8233,10 +8231,10 @@
     </row>
     <row r="248" spans="1:4">
       <c r="A248" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B248" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C248" t="s">
         <v>24</v>
@@ -8247,10 +8245,10 @@
     </row>
     <row r="249" spans="1:4">
       <c r="A249" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B249" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C249" t="s">
         <v>24</v>
@@ -8295,7 +8293,7 @@
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
-  <dimension ref="B1:D20"/>
+  <dimension ref="B1:D28"/>
   <sheetFormatPr defaultColWidth="15" defaultRowHeight="25.5"/>
   <cols>
     <col min="1" max="1" width="4.625" style="1" customWidth="1"/>
@@ -8347,7 +8345,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7" spans="2:4">
@@ -8355,7 +8353,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="49" t="s">
-        <v>55</v>
+        <v>1101</v>
       </c>
       <c r="D7" s="44"/>
     </row>
@@ -8465,9 +8463,12 @@
         <v>0</v>
       </c>
     </row>
+    <row r="28" spans="2:3">
+      <c r="C28" s="57"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="6">
+  <dataValidations disablePrompts="1" count="6">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C17" xr:uid="{E6D0CEF8-433B-44D1-9BB1-92BE13C5E787}">
       <formula1>"預設,上,右,上及右"</formula1>
     </dataValidation>
@@ -8624,7 +8625,7 @@
       <c r="R3" s="48"/>
       <c r="T3" s="15"/>
       <c r="V3" s="51" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="4" spans="1:22" s="6" customFormat="1" ht="36" customHeight="1">
@@ -8667,28 +8668,28 @@
         <v>35</v>
       </c>
       <c r="E5" s="54" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="F5" s="54" t="s">
+      <c r="G5" s="54" t="s">
         <v>60</v>
-      </c>
-      <c r="G5" s="54" t="s">
-        <v>61</v>
       </c>
       <c r="H5" s="54" t="s">
         <v>36</v>
       </c>
       <c r="I5" s="54" t="s">
+        <v>61</v>
+      </c>
+      <c r="J5" s="54" t="s">
         <v>62</v>
       </c>
-      <c r="J5" s="54" t="s">
+      <c r="K5" s="54" t="s">
         <v>63</v>
       </c>
-      <c r="K5" s="54" t="s">
+      <c r="L5" s="54" t="s">
         <v>64</v>
-      </c>
-      <c r="L5" s="54" t="s">
-        <v>65</v>
       </c>
       <c r="M5" s="54" t="str">
         <f>CHAR(10)</f>
@@ -8807,49 +8808,49 @@
         <v>2</v>
       </c>
       <c r="D9" s="54" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="E9" s="54" t="s">
-        <v>60</v>
-      </c>
       <c r="F9" s="54" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" s="54" t="s">
         <v>66</v>
       </c>
-      <c r="G9" s="54" t="s">
+      <c r="H9" s="54" t="s">
         <v>67</v>
-      </c>
-      <c r="H9" s="54" t="s">
-        <v>68</v>
       </c>
       <c r="I9" s="54" t="s">
         <v>18</v>
       </c>
       <c r="J9" s="54" t="s">
+        <v>68</v>
+      </c>
+      <c r="K9" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="K9" s="54" t="s">
+      <c r="L9" s="54" t="s">
         <v>70</v>
-      </c>
-      <c r="L9" s="54" t="s">
-        <v>71</v>
       </c>
       <c r="M9" s="54" t="s">
         <v>18</v>
       </c>
       <c r="N9" s="54" t="s">
+        <v>71</v>
+      </c>
+      <c r="O9" s="54" t="s">
         <v>72</v>
       </c>
-      <c r="O9" s="54" t="s">
+      <c r="P9" s="54" t="s">
         <v>73</v>
-      </c>
-      <c r="P9" s="54" t="s">
-        <v>74</v>
       </c>
       <c r="Q9" s="54" t="s">
         <v>18</v>
       </c>
       <c r="R9" s="54" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="S9" s="19"/>
       <c r="T9" s="15"/>
@@ -8971,49 +8972,49 @@
         <v>3</v>
       </c>
       <c r="D13" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="E13" s="54" t="s">
         <v>76</v>
       </c>
-      <c r="E13" s="54" t="s">
+      <c r="F13" s="54" t="s">
         <v>77</v>
       </c>
-      <c r="F13" s="54" t="s">
+      <c r="G13" s="54" t="s">
         <v>78</v>
       </c>
-      <c r="G13" s="54" t="s">
+      <c r="H13" s="54" t="s">
         <v>79</v>
       </c>
-      <c r="H13" s="54" t="s">
+      <c r="I13" s="54" t="s">
         <v>80</v>
-      </c>
-      <c r="I13" s="54" t="s">
-        <v>81</v>
       </c>
       <c r="J13" s="54" t="s">
         <v>18</v>
       </c>
       <c r="K13" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="L13" s="54" t="s">
         <v>70</v>
-      </c>
-      <c r="L13" s="54" t="s">
-        <v>71</v>
       </c>
       <c r="M13" s="54" t="s">
         <v>42</v>
       </c>
       <c r="N13" s="54" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="O13" s="54" t="s">
         <v>19</v>
       </c>
       <c r="P13" s="54" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q13" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="Q13" s="54" t="s">
-        <v>60</v>
-      </c>
       <c r="R13" s="54" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="S13" s="19"/>
       <c r="V13" s="52"/>
@@ -9137,43 +9138,43 @@
         <v>18</v>
       </c>
       <c r="E17" s="54" t="s">
+        <v>83</v>
+      </c>
+      <c r="F17" s="54" t="s">
         <v>84</v>
       </c>
-      <c r="F17" s="54" t="s">
+      <c r="G17" s="54" t="s">
         <v>85</v>
       </c>
-      <c r="G17" s="54" t="s">
+      <c r="H17" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="H17" s="54" t="s">
+      <c r="I17" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="I17" s="54" t="s">
+      <c r="J17" s="54" t="s">
         <v>88</v>
       </c>
-      <c r="J17" s="54" t="s">
+      <c r="K17" s="54" t="s">
         <v>89</v>
-      </c>
-      <c r="K17" s="54" t="s">
-        <v>90</v>
       </c>
       <c r="L17" s="54" t="s">
         <v>19</v>
       </c>
       <c r="M17" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="N17" s="54" t="s">
         <v>67</v>
       </c>
-      <c r="N17" s="54" t="s">
-        <v>68</v>
-      </c>
       <c r="O17" s="54" t="s">
+        <v>90</v>
+      </c>
+      <c r="P17" s="54" t="s">
         <v>91</v>
       </c>
-      <c r="P17" s="54" t="s">
+      <c r="Q17" s="54" t="s">
         <v>92</v>
-      </c>
-      <c r="Q17" s="54" t="s">
-        <v>93</v>
       </c>
       <c r="R17" s="54" t="s">
         <v>18</v>
@@ -9295,46 +9296,46 @@
         <v>5</v>
       </c>
       <c r="D21" s="54" t="s">
+        <v>93</v>
+      </c>
+      <c r="E21" s="54" t="s">
+        <v>67</v>
+      </c>
+      <c r="F21" s="54" t="s">
         <v>94</v>
       </c>
-      <c r="E21" s="54" t="s">
-        <v>68</v>
-      </c>
-      <c r="F21" s="54" t="s">
+      <c r="G21" s="54" t="s">
         <v>95</v>
       </c>
-      <c r="G21" s="54" t="s">
+      <c r="H21" s="54" t="s">
         <v>96</v>
-      </c>
-      <c r="H21" s="54" t="s">
-        <v>97</v>
       </c>
       <c r="I21" s="54" t="s">
         <v>18</v>
       </c>
       <c r="J21" s="54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K21" s="54" t="s">
+        <v>97</v>
+      </c>
+      <c r="L21" s="54" t="s">
         <v>98</v>
       </c>
-      <c r="L21" s="54" t="s">
+      <c r="M21" s="54" t="s">
         <v>99</v>
-      </c>
-      <c r="M21" s="54" t="s">
-        <v>100</v>
       </c>
       <c r="N21" s="54" t="s">
         <v>18</v>
       </c>
       <c r="O21" s="54" t="s">
+        <v>100</v>
+      </c>
+      <c r="P21" s="54" t="s">
         <v>101</v>
       </c>
-      <c r="P21" s="54" t="s">
-        <v>102</v>
-      </c>
       <c r="Q21" s="54" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="R21" s="54" t="s">
         <v>18</v>
@@ -9440,16 +9441,16 @@
         <v>6</v>
       </c>
       <c r="D25" s="54" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E25" s="54" t="s">
+        <v>102</v>
+      </c>
+      <c r="F25" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="F25" s="54" t="s">
+      <c r="G25" s="54" t="s">
         <v>104</v>
-      </c>
-      <c r="G25" s="54" t="s">
-        <v>105</v>
       </c>
       <c r="H25" s="54" t="s">
         <v>19</v>
@@ -9579,49 +9580,49 @@
         <v>7</v>
       </c>
       <c r="D29" s="54" t="s">
+        <v>105</v>
+      </c>
+      <c r="E29" s="54" t="s">
         <v>106</v>
       </c>
-      <c r="E29" s="54" t="s">
+      <c r="F29" s="54" t="s">
         <v>107</v>
       </c>
-      <c r="F29" s="54" t="s">
+      <c r="G29" s="54" t="s">
         <v>108</v>
-      </c>
-      <c r="G29" s="54" t="s">
-        <v>109</v>
       </c>
       <c r="H29" s="54" t="s">
         <v>18</v>
       </c>
       <c r="I29" s="54" t="s">
+        <v>109</v>
+      </c>
+      <c r="J29" s="54" t="s">
+        <v>108</v>
+      </c>
+      <c r="K29" s="54" t="s">
+        <v>91</v>
+      </c>
+      <c r="L29" s="54" t="s">
+        <v>108</v>
+      </c>
+      <c r="M29" s="54" t="s">
+        <v>107</v>
+      </c>
+      <c r="N29" s="54" t="s">
         <v>110</v>
-      </c>
-      <c r="J29" s="54" t="s">
-        <v>109</v>
-      </c>
-      <c r="K29" s="54" t="s">
-        <v>92</v>
-      </c>
-      <c r="L29" s="54" t="s">
-        <v>109</v>
-      </c>
-      <c r="M29" s="54" t="s">
-        <v>108</v>
-      </c>
-      <c r="N29" s="54" t="s">
-        <v>111</v>
       </c>
       <c r="O29" s="54" t="s">
         <v>18</v>
       </c>
       <c r="P29" s="54" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q29" s="54" t="s">
         <v>112</v>
       </c>
-      <c r="Q29" s="54" t="s">
+      <c r="R29" s="54" t="s">
         <v>113</v>
-      </c>
-      <c r="R29" s="54" t="s">
-        <v>114</v>
       </c>
       <c r="S29" s="19"/>
       <c r="U29" s="32" t="str">
@@ -9758,25 +9759,25 @@
         <v>8</v>
       </c>
       <c r="D33" s="54" t="s">
+        <v>114</v>
+      </c>
+      <c r="E33" s="54" t="s">
         <v>115</v>
       </c>
-      <c r="E33" s="54" t="s">
+      <c r="F33" s="54" t="s">
         <v>116</v>
       </c>
-      <c r="F33" s="54" t="s">
+      <c r="G33" s="54" t="s">
         <v>117</v>
       </c>
-      <c r="G33" s="54" t="s">
+      <c r="H33" s="54" t="s">
+        <v>97</v>
+      </c>
+      <c r="I33" s="54" t="s">
+        <v>107</v>
+      </c>
+      <c r="J33" s="54" t="s">
         <v>118</v>
-      </c>
-      <c r="H33" s="54" t="s">
-        <v>98</v>
-      </c>
-      <c r="I33" s="54" t="s">
-        <v>108</v>
-      </c>
-      <c r="J33" s="54" t="s">
-        <v>119</v>
       </c>
       <c r="K33" s="54" t="s">
         <v>18</v>
@@ -9785,19 +9786,19 @@
         <v>42</v>
       </c>
       <c r="M33" s="54" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N33" s="54" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O33" s="54" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P33" s="54" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q33" s="54" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="R33" s="54" t="s">
         <v>18</v>
@@ -9921,46 +9922,46 @@
         <v>9</v>
       </c>
       <c r="D37" s="54" t="s">
+        <v>119</v>
+      </c>
+      <c r="E37" s="54" t="s">
+        <v>112</v>
+      </c>
+      <c r="F37" s="54" t="s">
+        <v>113</v>
+      </c>
+      <c r="G37" s="54" t="s">
+        <v>114</v>
+      </c>
+      <c r="H37" s="54" t="s">
+        <v>115</v>
+      </c>
+      <c r="I37" s="54" t="s">
         <v>120</v>
-      </c>
-      <c r="E37" s="54" t="s">
-        <v>113</v>
-      </c>
-      <c r="F37" s="54" t="s">
-        <v>114</v>
-      </c>
-      <c r="G37" s="54" t="s">
-        <v>115</v>
-      </c>
-      <c r="H37" s="54" t="s">
-        <v>116</v>
-      </c>
-      <c r="I37" s="54" t="s">
-        <v>121</v>
       </c>
       <c r="J37" s="54" t="s">
         <v>19</v>
       </c>
       <c r="K37" s="54" t="s">
+        <v>121</v>
+      </c>
+      <c r="L37" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="M37" s="54" t="s">
+        <v>107</v>
+      </c>
+      <c r="N37" s="54" t="s">
         <v>122</v>
       </c>
-      <c r="L37" s="54" t="s">
-        <v>78</v>
-      </c>
-      <c r="M37" s="54" t="s">
-        <v>108</v>
-      </c>
-      <c r="N37" s="54" t="s">
+      <c r="O37" s="54" t="s">
         <v>123</v>
-      </c>
-      <c r="O37" s="54" t="s">
-        <v>124</v>
       </c>
       <c r="P37" s="54" t="s">
         <v>18</v>
       </c>
       <c r="Q37" s="54" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="R37" s="54" t="s">
         <v>42</v>
@@ -10084,49 +10085,49 @@
         <v>10</v>
       </c>
       <c r="D41" s="54" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E41" s="54" t="s">
+        <v>58</v>
+      </c>
+      <c r="F41" s="54" t="s">
         <v>59</v>
-      </c>
-      <c r="F41" s="54" t="s">
-        <v>60</v>
       </c>
       <c r="G41" s="54" t="s">
         <v>18</v>
       </c>
       <c r="H41" s="54" t="s">
+        <v>126</v>
+      </c>
+      <c r="I41" s="54" t="s">
+        <v>125</v>
+      </c>
+      <c r="J41" s="54" t="s">
         <v>127</v>
       </c>
-      <c r="I41" s="54" t="s">
-        <v>126</v>
-      </c>
-      <c r="J41" s="54" t="s">
+      <c r="K41" s="54" t="s">
         <v>128</v>
-      </c>
-      <c r="K41" s="54" t="s">
-        <v>129</v>
       </c>
       <c r="L41" s="54" t="s">
         <v>19</v>
       </c>
       <c r="M41" s="54" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="N41" s="54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O41" s="54" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P41" s="54" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q41" s="54" t="s">
         <v>18</v>
       </c>
       <c r="R41" s="54" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="S41" s="19"/>
       <c r="V41" s="52"/>
@@ -10250,46 +10251,46 @@
         <v>42</v>
       </c>
       <c r="E45" s="54" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F45" s="54" t="s">
+        <v>83</v>
+      </c>
+      <c r="G45" s="54" t="s">
         <v>84</v>
       </c>
-      <c r="G45" s="54" t="s">
+      <c r="H45" s="54" t="s">
         <v>85</v>
       </c>
-      <c r="H45" s="54" t="s">
+      <c r="I45" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="I45" s="54" t="s">
+      <c r="J45" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="J45" s="54" t="s">
+      <c r="K45" s="54" t="s">
         <v>88</v>
-      </c>
-      <c r="K45" s="54" t="s">
-        <v>89</v>
       </c>
       <c r="L45" s="54" t="s">
         <v>18</v>
       </c>
       <c r="M45" s="54" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N45" s="54" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="O45" s="54" t="s">
+        <v>58</v>
+      </c>
+      <c r="P45" s="54" t="s">
         <v>59</v>
-      </c>
-      <c r="P45" s="54" t="s">
-        <v>60</v>
       </c>
       <c r="Q45" s="54" t="s">
         <v>19</v>
       </c>
       <c r="R45" s="54" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="S45" s="19"/>
       <c r="V45" s="52"/>
@@ -10412,46 +10413,46 @@
         <v>12</v>
       </c>
       <c r="D49" s="54" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E49" s="54" t="s">
         <v>39</v>
       </c>
       <c r="F49" s="54" t="s">
+        <v>83</v>
+      </c>
+      <c r="G49" s="54" t="s">
         <v>84</v>
       </c>
-      <c r="G49" s="54" t="s">
+      <c r="H49" s="54" t="s">
         <v>85</v>
       </c>
-      <c r="H49" s="54" t="s">
+      <c r="I49" s="54" t="s">
         <v>86</v>
       </c>
-      <c r="I49" s="54" t="s">
+      <c r="J49" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="J49" s="54" t="s">
+      <c r="K49" s="54" t="s">
         <v>88</v>
       </c>
-      <c r="K49" s="54" t="s">
-        <v>89</v>
-      </c>
       <c r="L49" s="54" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M49" s="54" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N49" s="54" t="s">
         <v>18</v>
       </c>
       <c r="O49" s="54" t="s">
+        <v>133</v>
+      </c>
+      <c r="P49" s="54" t="s">
         <v>134</v>
       </c>
-      <c r="P49" s="54" t="s">
-        <v>135</v>
-      </c>
       <c r="Q49" s="54" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R49" s="54" t="s">
         <v>20</v>
@@ -10577,49 +10578,49 @@
         <v>13</v>
       </c>
       <c r="D53" s="54" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E53" s="54" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F53" s="54" t="s">
         <v>18</v>
       </c>
       <c r="G53" s="54" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H53" s="54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I53" s="54" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J53" s="54" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K53" s="54" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L53" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="M53" s="54" t="s">
         <v>67</v>
       </c>
-      <c r="M53" s="54" t="s">
-        <v>68</v>
-      </c>
       <c r="N53" s="54" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O53" s="54" t="s">
         <v>19</v>
       </c>
       <c r="P53" s="54" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q53" s="54" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="R53" s="54" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="S53" s="19"/>
       <c r="V53" s="52"/>
@@ -10744,49 +10745,49 @@
         <v>14</v>
       </c>
       <c r="D57" s="54" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E57" s="54" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F57" s="54" t="s">
         <v>38</v>
       </c>
       <c r="G57" s="54" t="s">
+        <v>139</v>
+      </c>
+      <c r="H57" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="H57" s="54" t="s">
+      <c r="I57" s="54" t="s">
         <v>141</v>
-      </c>
-      <c r="I57" s="54" t="s">
-        <v>142</v>
       </c>
       <c r="J57" s="54" t="s">
         <v>18</v>
       </c>
       <c r="K57" s="54" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L57" s="54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M57" s="54" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N57" s="54" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O57" s="54" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P57" s="54" t="s">
         <v>38</v>
       </c>
       <c r="Q57" s="54" t="s">
+        <v>143</v>
+      </c>
+      <c r="R57" s="54" t="s">
         <v>144</v>
-      </c>
-      <c r="R57" s="54" t="s">
-        <v>145</v>
       </c>
       <c r="S57" s="19"/>
       <c r="V57" s="52"/>
@@ -10911,49 +10912,49 @@
         <v>15</v>
       </c>
       <c r="D61" s="54" t="s">
+        <v>145</v>
+      </c>
+      <c r="E61" s="54" t="s">
         <v>146</v>
       </c>
-      <c r="E61" s="54" t="s">
-        <v>147</v>
-      </c>
       <c r="F61" s="54" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G61" s="54" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H61" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="I61" s="54" t="s">
         <v>67</v>
       </c>
-      <c r="I61" s="54" t="s">
-        <v>68</v>
-      </c>
       <c r="J61" s="54" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K61" s="54" t="s">
         <v>20</v>
       </c>
       <c r="L61" s="54" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M61" s="54" t="s">
         <v>39</v>
       </c>
       <c r="N61" s="54" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O61" s="54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P61" s="54" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Q61" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="R61" s="54" t="s">
         <v>67</v>
-      </c>
-      <c r="R61" s="54" t="s">
-        <v>68</v>
       </c>
       <c r="S61" s="19"/>
       <c r="V61" s="52"/>
@@ -11066,31 +11067,31 @@
         <v>16</v>
       </c>
       <c r="D65" s="54" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E65" s="54" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F65" s="54" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G65" s="54" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H65" s="54" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I65" s="54" t="s">
         <v>18</v>
       </c>
       <c r="J65" s="54" t="s">
+        <v>58</v>
+      </c>
+      <c r="K65" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="K65" s="54" t="s">
-        <v>60</v>
-      </c>
       <c r="L65" s="54" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M65" s="54" t="s">
         <v>19</v>
@@ -11213,46 +11214,46 @@
         <v>17</v>
       </c>
       <c r="D69" s="54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E69" s="54" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F69" s="54" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G69" s="54" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H69" s="54" t="s">
         <v>18</v>
       </c>
       <c r="I69" s="54" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J69" s="54" t="s">
         <v>43</v>
       </c>
       <c r="K69" s="54" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L69" s="54" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M69" s="54" t="s">
         <v>39</v>
       </c>
       <c r="N69" s="54" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O69" s="54" t="s">
         <v>40</v>
       </c>
       <c r="P69" s="54" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q69" s="54" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R69" s="54" t="s">
         <v>18</v>
@@ -11378,49 +11379,49 @@
         <v>18</v>
       </c>
       <c r="D73" s="54" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E73" s="54" t="s">
+        <v>152</v>
+      </c>
+      <c r="F73" s="54" t="s">
+        <v>59</v>
+      </c>
+      <c r="G73" s="54" t="s">
         <v>153</v>
       </c>
-      <c r="F73" s="54" t="s">
-        <v>60</v>
-      </c>
-      <c r="G73" s="54" t="s">
+      <c r="H73" s="54" t="s">
         <v>154</v>
       </c>
-      <c r="H73" s="54" t="s">
+      <c r="I73" s="54" t="s">
         <v>155</v>
       </c>
-      <c r="I73" s="54" t="s">
+      <c r="J73" s="54" t="s">
         <v>156</v>
       </c>
-      <c r="J73" s="54" t="s">
+      <c r="K73" s="54" t="s">
+        <v>107</v>
+      </c>
+      <c r="L73" s="54" t="s">
         <v>157</v>
       </c>
-      <c r="K73" s="54" t="s">
-        <v>108</v>
-      </c>
-      <c r="L73" s="54" t="s">
+      <c r="M73" s="54" t="s">
+        <v>135</v>
+      </c>
+      <c r="N73" s="54" t="s">
+        <v>152</v>
+      </c>
+      <c r="O73" s="54" t="s">
         <v>158</v>
-      </c>
-      <c r="M73" s="54" t="s">
-        <v>136</v>
-      </c>
-      <c r="N73" s="54" t="s">
-        <v>153</v>
-      </c>
-      <c r="O73" s="54" t="s">
-        <v>159</v>
       </c>
       <c r="P73" s="54" t="s">
         <v>18</v>
       </c>
       <c r="Q73" s="54" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R73" s="54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="S73" s="19"/>
       <c r="V73" s="52"/>
@@ -11541,49 +11542,49 @@
         <v>19</v>
       </c>
       <c r="D77" s="54" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E77" s="54" t="s">
         <v>18</v>
       </c>
       <c r="F77" s="54" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G77" s="54" t="s">
         <v>42</v>
       </c>
       <c r="H77" s="54" t="s">
+        <v>161</v>
+      </c>
+      <c r="I77" s="54" t="s">
+        <v>125</v>
+      </c>
+      <c r="J77" s="54" t="s">
+        <v>62</v>
+      </c>
+      <c r="K77" s="54" t="s">
         <v>162</v>
       </c>
-      <c r="I77" s="54" t="s">
-        <v>126</v>
-      </c>
-      <c r="J77" s="54" t="s">
-        <v>63</v>
-      </c>
-      <c r="K77" s="54" t="s">
+      <c r="L77" s="54" t="s">
+        <v>83</v>
+      </c>
+      <c r="M77" s="54" t="s">
+        <v>84</v>
+      </c>
+      <c r="N77" s="54" t="s">
+        <v>85</v>
+      </c>
+      <c r="O77" s="54" t="s">
+        <v>86</v>
+      </c>
+      <c r="P77" s="54" t="s">
         <v>163</v>
       </c>
-      <c r="L77" s="54" t="s">
-        <v>84</v>
-      </c>
-      <c r="M77" s="54" t="s">
-        <v>85</v>
-      </c>
-      <c r="N77" s="54" t="s">
-        <v>86</v>
-      </c>
-      <c r="O77" s="54" t="s">
+      <c r="Q77" s="54" t="s">
         <v>87</v>
       </c>
-      <c r="P77" s="54" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q77" s="54" t="s">
+      <c r="R77" s="54" t="s">
         <v>88</v>
-      </c>
-      <c r="R77" s="54" t="s">
-        <v>89</v>
       </c>
       <c r="S77" s="19"/>
       <c r="V77" s="52"/>
@@ -11700,19 +11701,19 @@
         <v>20</v>
       </c>
       <c r="D81" s="54" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E81" s="54" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F81" s="54" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G81" s="54" t="s">
         <v>20</v>
       </c>
       <c r="H81" s="54" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I81" s="54" t="s">
         <v>18</v>
@@ -11721,28 +11722,28 @@
         <v>42</v>
       </c>
       <c r="K81" s="54" t="s">
+        <v>165</v>
+      </c>
+      <c r="L81" s="54" t="s">
         <v>166</v>
       </c>
-      <c r="L81" s="54" t="s">
+      <c r="M81" s="54" t="s">
         <v>167</v>
       </c>
-      <c r="M81" s="54" t="s">
+      <c r="N81" s="54" t="s">
+        <v>126</v>
+      </c>
+      <c r="O81" s="54" t="s">
         <v>168</v>
-      </c>
-      <c r="N81" s="54" t="s">
-        <v>127</v>
-      </c>
-      <c r="O81" s="54" t="s">
-        <v>169</v>
       </c>
       <c r="P81" s="54" t="s">
         <v>19</v>
       </c>
       <c r="Q81" s="54" t="s">
+        <v>169</v>
+      </c>
+      <c r="R81" s="54" t="s">
         <v>170</v>
-      </c>
-      <c r="R81" s="54" t="s">
-        <v>171</v>
       </c>
       <c r="S81" s="19"/>
       <c r="V81" s="52"/>
@@ -11863,46 +11864,46 @@
         <v>21</v>
       </c>
       <c r="D85" s="54" t="s">
+        <v>171</v>
+      </c>
+      <c r="E85" s="54" t="s">
+        <v>59</v>
+      </c>
+      <c r="F85" s="54" t="s">
+        <v>152</v>
+      </c>
+      <c r="G85" s="54" t="s">
         <v>172</v>
       </c>
-      <c r="E85" s="54" t="s">
-        <v>60</v>
-      </c>
-      <c r="F85" s="54" t="s">
-        <v>153</v>
-      </c>
-      <c r="G85" s="54" t="s">
+      <c r="H85" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="I85" s="54" t="s">
+        <v>67</v>
+      </c>
+      <c r="J85" s="54" t="s">
         <v>173</v>
       </c>
-      <c r="H85" s="54" t="s">
-        <v>67</v>
-      </c>
-      <c r="I85" s="54" t="s">
-        <v>68</v>
-      </c>
-      <c r="J85" s="54" t="s">
+      <c r="K85" s="54" t="s">
         <v>174</v>
-      </c>
-      <c r="K85" s="54" t="s">
-        <v>175</v>
       </c>
       <c r="L85" s="54" t="s">
         <v>42</v>
       </c>
       <c r="M85" s="54" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N85" s="54" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="O85" s="54" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P85" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q85" s="54" t="s">
         <v>176</v>
-      </c>
-      <c r="Q85" s="54" t="s">
-        <v>177</v>
       </c>
       <c r="R85" s="54" t="s">
         <v>39</v>
@@ -12030,49 +12031,49 @@
         <v>22</v>
       </c>
       <c r="D89" s="54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E89" s="54" t="s">
+        <v>177</v>
+      </c>
+      <c r="F89" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="G89" s="54" t="s">
+        <v>67</v>
+      </c>
+      <c r="H89" s="54" t="s">
         <v>178</v>
       </c>
-      <c r="F89" s="54" t="s">
-        <v>67</v>
-      </c>
-      <c r="G89" s="54" t="s">
-        <v>68</v>
-      </c>
-      <c r="H89" s="54" t="s">
+      <c r="I89" s="54" t="s">
         <v>179</v>
       </c>
-      <c r="I89" s="54" t="s">
+      <c r="J89" s="54" t="s">
         <v>180</v>
       </c>
-      <c r="J89" s="54" t="s">
-        <v>181</v>
-      </c>
       <c r="K89" s="54" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L89" s="54" t="s">
         <v>18</v>
       </c>
       <c r="M89" s="54" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N89" s="54" t="s">
         <v>38</v>
       </c>
       <c r="O89" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="P89" s="54" t="s">
         <v>67</v>
       </c>
-      <c r="P89" s="54" t="s">
-        <v>68</v>
-      </c>
       <c r="Q89" s="54" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="R89" s="54" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="S89" s="19"/>
       <c r="V89" s="7"/>
@@ -12200,46 +12201,46 @@
         <v>20</v>
       </c>
       <c r="E93" s="54" t="s">
+        <v>175</v>
+      </c>
+      <c r="F93" s="54" t="s">
         <v>176</v>
       </c>
-      <c r="F93" s="54" t="s">
-        <v>177</v>
-      </c>
       <c r="G93" s="54" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H93" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="I93" s="54" t="s">
         <v>67</v>
       </c>
-      <c r="I93" s="54" t="s">
-        <v>68</v>
-      </c>
       <c r="J93" s="54" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K93" s="54" t="s">
         <v>42</v>
       </c>
       <c r="L93" s="54" t="s">
+        <v>182</v>
+      </c>
+      <c r="M93" s="54" t="s">
+        <v>176</v>
+      </c>
+      <c r="N93" s="54" t="s">
         <v>183</v>
-      </c>
-      <c r="M93" s="54" t="s">
-        <v>177</v>
-      </c>
-      <c r="N93" s="54" t="s">
-        <v>184</v>
       </c>
       <c r="O93" s="54" t="s">
         <v>18</v>
       </c>
       <c r="P93" s="54" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q93" s="54" t="s">
         <v>42</v>
       </c>
       <c r="R93" s="54" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S93" s="19"/>
       <c r="V93" s="7"/>
@@ -12360,49 +12361,49 @@
         <v>24</v>
       </c>
       <c r="D97" s="54" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E97" s="54" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F97" s="54" t="s">
         <v>18</v>
       </c>
       <c r="G97" s="54" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H97" s="54" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="I97" s="54" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="J97" s="54" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K97" s="54" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L97" s="54" t="s">
         <v>18</v>
       </c>
       <c r="M97" s="54" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="N97" s="54" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O97" s="54" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P97" s="54" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q97" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="R97" s="54" t="s">
         <v>187</v>
-      </c>
-      <c r="Q97" s="54" t="s">
-        <v>76</v>
-      </c>
-      <c r="R97" s="54" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="98" spans="2:18" s="6" customFormat="1" ht="36" customHeight="1">
@@ -12521,46 +12522,46 @@
         <v>19</v>
       </c>
       <c r="E101" s="54" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F101" s="54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G101" s="54" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H101" s="54" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I101" s="54" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="J101" s="54" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K101" s="54" t="s">
         <v>42</v>
       </c>
       <c r="L101" s="54" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M101" s="54" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="N101" s="54" t="s">
         <v>18</v>
       </c>
       <c r="O101" s="54" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P101" s="54" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q101" s="54" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="R101" s="54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="102" spans="2:18" s="6" customFormat="1" ht="36" customHeight="1">
@@ -12676,49 +12677,49 @@
         <v>26</v>
       </c>
       <c r="D105" s="54" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E105" s="54" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F105" s="54" t="s">
         <v>19</v>
       </c>
       <c r="G105" s="54" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H105" s="54" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="I105" s="54" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="J105" s="54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K105" s="54" t="s">
         <v>18</v>
       </c>
       <c r="L105" s="54" t="s">
+        <v>131</v>
+      </c>
+      <c r="M105" s="54" t="s">
         <v>132</v>
       </c>
-      <c r="M105" s="54" t="s">
-        <v>133</v>
-      </c>
       <c r="N105" s="54" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O105" s="54" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P105" s="54" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q105" s="54" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="R105" s="54" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="106" spans="2:18" s="6" customFormat="1" ht="36" customHeight="1">
@@ -12834,49 +12835,49 @@
         <v>27</v>
       </c>
       <c r="D109" s="54" t="s">
+        <v>193</v>
+      </c>
+      <c r="E109" s="54" t="s">
+        <v>65</v>
+      </c>
+      <c r="F109" s="54" t="s">
         <v>194</v>
       </c>
-      <c r="E109" s="54" t="s">
-        <v>66</v>
-      </c>
-      <c r="F109" s="54" t="s">
-        <v>195</v>
-      </c>
       <c r="G109" s="54" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H109" s="54" t="s">
         <v>19</v>
       </c>
       <c r="I109" s="54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J109" s="54" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K109" s="54" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L109" s="54" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M109" s="54" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N109" s="54" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O109" s="54" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P109" s="54" t="s">
         <v>18</v>
       </c>
       <c r="Q109" s="54" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R109" s="54" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="110" spans="2:18" s="6" customFormat="1" ht="36" customHeight="1">
@@ -12995,49 +12996,49 @@
         <v>28</v>
       </c>
       <c r="D113" s="54" t="s">
+        <v>196</v>
+      </c>
+      <c r="E113" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="F113" s="54" t="s">
+        <v>67</v>
+      </c>
+      <c r="G113" s="54" t="s">
+        <v>107</v>
+      </c>
+      <c r="H113" s="54" t="s">
         <v>197</v>
       </c>
-      <c r="E113" s="54" t="s">
-        <v>67</v>
-      </c>
-      <c r="F113" s="54" t="s">
-        <v>68</v>
-      </c>
-      <c r="G113" s="54" t="s">
-        <v>108</v>
-      </c>
-      <c r="H113" s="54" t="s">
+      <c r="I113" s="54" t="s">
         <v>198</v>
       </c>
-      <c r="I113" s="54" t="s">
+      <c r="J113" s="54" t="s">
         <v>199</v>
-      </c>
-      <c r="J113" s="54" t="s">
-        <v>200</v>
       </c>
       <c r="K113" s="54" t="s">
         <v>39</v>
       </c>
       <c r="L113" s="54" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M113" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="N113" s="54" t="s">
         <v>78</v>
-      </c>
-      <c r="N113" s="54" t="s">
-        <v>79</v>
       </c>
       <c r="O113" s="54" t="s">
         <v>42</v>
       </c>
       <c r="P113" s="54" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q113" s="54" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="R113" s="54" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="114" spans="2:18" s="6" customFormat="1" ht="36" customHeight="1">
@@ -13151,46 +13152,46 @@
         <v>29</v>
       </c>
       <c r="D117" s="54" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E117" s="54" t="s">
         <v>18</v>
       </c>
       <c r="F117" s="54" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G117" s="54" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H117" s="54" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I117" s="54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J117" s="54" t="s">
         <v>18</v>
       </c>
       <c r="K117" s="54" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L117" s="54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M117" s="54" t="s">
         <v>18</v>
       </c>
       <c r="N117" s="54" t="s">
+        <v>131</v>
+      </c>
+      <c r="O117" s="54" t="s">
         <v>132</v>
       </c>
-      <c r="O117" s="54" t="s">
-        <v>133</v>
-      </c>
       <c r="P117" s="54" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="Q117" s="54" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="R117" s="54" t="s">
         <v>18</v>
@@ -13305,16 +13306,16 @@
         <v>30</v>
       </c>
       <c r="D121" s="54" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E121" s="54" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F121" s="54" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G121" s="54" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H121" s="54" t="s">
         <v>19</v>
@@ -13323,31 +13324,31 @@
         <v>42</v>
       </c>
       <c r="J121" s="54" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="K121" s="54" t="s">
         <v>18</v>
       </c>
       <c r="L121" s="54" t="s">
+        <v>155</v>
+      </c>
+      <c r="M121" s="54" t="s">
         <v>156</v>
       </c>
-      <c r="M121" s="54" t="s">
-        <v>157</v>
-      </c>
       <c r="N121" s="54" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O121" s="54" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P121" s="54" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Q121" s="54" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="R121" s="54" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="122" spans="2:18" s="6" customFormat="1" ht="36" customHeight="1">
@@ -13461,43 +13462,43 @@
         <v>31</v>
       </c>
       <c r="D125" s="54" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E125" s="54" t="s">
         <v>39</v>
       </c>
       <c r="F125" s="54" t="s">
+        <v>204</v>
+      </c>
+      <c r="G125" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="H125" s="54" t="s">
+        <v>67</v>
+      </c>
+      <c r="I125" s="54" t="s">
         <v>205</v>
       </c>
-      <c r="G125" s="54" t="s">
-        <v>67</v>
-      </c>
-      <c r="H125" s="54" t="s">
-        <v>68</v>
-      </c>
-      <c r="I125" s="54" t="s">
+      <c r="J125" s="54" t="s">
+        <v>126</v>
+      </c>
+      <c r="K125" s="54" t="s">
         <v>206</v>
       </c>
-      <c r="J125" s="54" t="s">
-        <v>127</v>
-      </c>
-      <c r="K125" s="54" t="s">
-        <v>207</v>
-      </c>
       <c r="L125" s="54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M125" s="54" t="s">
         <v>18</v>
       </c>
       <c r="N125" s="54" t="s">
+        <v>207</v>
+      </c>
+      <c r="O125" s="54" t="s">
         <v>208</v>
       </c>
-      <c r="O125" s="54" t="s">
-        <v>209</v>
-      </c>
       <c r="P125" s="54" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="Q125" s="54" t="s">
         <v>20</v>
@@ -13617,49 +13618,49 @@
         <v>32</v>
       </c>
       <c r="D129" s="54" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E129" s="54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F129" s="54" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G129" s="54" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H129" s="54" t="s">
         <v>18</v>
       </c>
       <c r="I129" s="54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J129" s="54" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K129" s="54" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="L129" s="54" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M129" s="54" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N129" s="54" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="O129" s="54" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P129" s="54" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q129" s="54" t="s">
         <v>39</v>
       </c>
       <c r="R129" s="54" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="130" spans="2:18" s="6" customFormat="1" ht="36" customHeight="1">
@@ -13775,19 +13776,19 @@
         <v>33</v>
       </c>
       <c r="D133" s="54" t="s">
+        <v>170</v>
+      </c>
+      <c r="E133" s="54" t="s">
         <v>171</v>
       </c>
-      <c r="E133" s="54" t="s">
-        <v>172</v>
-      </c>
       <c r="F133" s="54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G133" s="54" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H133" s="54" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I133" s="54" t="s">
         <v>42</v>
@@ -13796,28 +13797,28 @@
         <v>38</v>
       </c>
       <c r="K133" s="54" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="L133" s="54" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M133" s="54" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="N133" s="54" t="s">
         <v>19</v>
       </c>
       <c r="O133" s="54" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="P133" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q133" s="54" t="s">
         <v>67</v>
       </c>
-      <c r="Q133" s="54" t="s">
-        <v>68</v>
-      </c>
       <c r="R133" s="54" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="134" spans="2:18" s="6" customFormat="1" ht="36" customHeight="1">
@@ -13939,43 +13940,43 @@
         <v>18</v>
       </c>
       <c r="F137" s="54" t="s">
+        <v>154</v>
+      </c>
+      <c r="G137" s="54" t="s">
         <v>155</v>
       </c>
-      <c r="G137" s="54" t="s">
+      <c r="H137" s="54" t="s">
         <v>156</v>
       </c>
-      <c r="H137" s="54" t="s">
+      <c r="I137" s="54" t="s">
+        <v>107</v>
+      </c>
+      <c r="J137" s="54" t="s">
         <v>157</v>
       </c>
-      <c r="I137" s="54" t="s">
-        <v>108</v>
-      </c>
-      <c r="J137" s="54" t="s">
-        <v>158</v>
-      </c>
       <c r="K137" s="54" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L137" s="54" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="M137" s="54" t="s">
+        <v>214</v>
+      </c>
+      <c r="N137" s="54" t="s">
         <v>215</v>
-      </c>
-      <c r="N137" s="54" t="s">
-        <v>216</v>
       </c>
       <c r="O137" s="54" t="s">
         <v>18</v>
       </c>
       <c r="P137" s="54" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q137" s="54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R137" s="54" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="138" spans="2:18" s="6" customFormat="1" ht="36" customHeight="1">
@@ -14091,49 +14092,49 @@
         <v>35</v>
       </c>
       <c r="D141" s="54" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E141" s="54" t="s">
         <v>18</v>
       </c>
       <c r="F141" s="54" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G141" s="54" t="s">
+        <v>77</v>
+      </c>
+      <c r="H141" s="54" t="s">
         <v>78</v>
       </c>
-      <c r="H141" s="54" t="s">
-        <v>79</v>
-      </c>
       <c r="I141" s="54" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J141" s="54" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K141" s="54" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L141" s="54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M141" s="54" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N141" s="54" t="s">
         <v>19</v>
       </c>
       <c r="O141" s="54" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P141" s="54" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="Q141" s="54" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R141" s="54" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="142" spans="2:18" s="6" customFormat="1" ht="36" customHeight="1">
@@ -14235,10 +14236,10 @@
         <v>36</v>
       </c>
       <c r="D145" s="54" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E145" s="54" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F145" s="54" t="s">
         <v>39</v>
@@ -14247,13 +14248,13 @@
         <v>42</v>
       </c>
       <c r="H145" s="54" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I145" s="54" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J145" s="54" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K145" s="54" t="s">
         <v>19</v>
@@ -14369,40 +14370,40 @@
         <v>37</v>
       </c>
       <c r="D149" s="54" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E149" s="54" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F149" s="54" t="s">
+        <v>217</v>
+      </c>
+      <c r="G149" s="54" t="s">
         <v>218</v>
       </c>
-      <c r="G149" s="54" t="s">
+      <c r="H149" s="54" t="s">
+        <v>91</v>
+      </c>
+      <c r="I149" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="J149" s="54" t="s">
         <v>219</v>
-      </c>
-      <c r="H149" s="54" t="s">
-        <v>92</v>
-      </c>
-      <c r="I149" s="54" t="s">
-        <v>67</v>
-      </c>
-      <c r="J149" s="54" t="s">
-        <v>220</v>
       </c>
       <c r="K149" s="54" t="s">
         <v>18</v>
       </c>
       <c r="L149" s="54" t="s">
+        <v>219</v>
+      </c>
+      <c r="M149" s="54" t="s">
+        <v>67</v>
+      </c>
+      <c r="N149" s="54" t="s">
+        <v>107</v>
+      </c>
+      <c r="O149" s="54" t="s">
         <v>220</v>
-      </c>
-      <c r="M149" s="54" t="s">
-        <v>68</v>
-      </c>
-      <c r="N149" s="54" t="s">
-        <v>108</v>
-      </c>
-      <c r="O149" s="54" t="s">
-        <v>221</v>
       </c>
       <c r="P149" s="54" t="s">
         <v>18</v>
@@ -14411,7 +14412,7 @@
         <v>42</v>
       </c>
       <c r="R149" s="54" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="150" spans="2:18" s="6" customFormat="1" ht="36" customHeight="1">
@@ -14527,49 +14528,49 @@
         <v>38</v>
       </c>
       <c r="D153" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="E153" s="54" t="s">
         <v>67</v>
-      </c>
-      <c r="E153" s="54" t="s">
-        <v>68</v>
       </c>
       <c r="F153" s="54" t="s">
         <v>18</v>
       </c>
       <c r="G153" s="54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H153" s="54" t="s">
+        <v>221</v>
+      </c>
+      <c r="I153" s="54" t="s">
         <v>222</v>
       </c>
-      <c r="I153" s="54" t="s">
+      <c r="J153" s="54" t="s">
         <v>223</v>
-      </c>
-      <c r="J153" s="54" t="s">
-        <v>224</v>
       </c>
       <c r="K153" s="54" t="s">
         <v>42</v>
       </c>
       <c r="L153" s="54" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="M153" s="54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N153" s="54" t="s">
         <v>19</v>
       </c>
       <c r="O153" s="54" t="s">
+        <v>224</v>
+      </c>
+      <c r="P153" s="54" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q153" s="54" t="s">
+        <v>107</v>
+      </c>
+      <c r="R153" s="54" t="s">
         <v>225</v>
-      </c>
-      <c r="P153" s="54" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q153" s="54" t="s">
-        <v>108</v>
-      </c>
-      <c r="R153" s="54" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="154" spans="2:18" s="6" customFormat="1" ht="36" customHeight="1">
@@ -14689,43 +14690,43 @@
         <v>42</v>
       </c>
       <c r="F157" s="54" t="s">
+        <v>226</v>
+      </c>
+      <c r="G157" s="54" t="s">
         <v>227</v>
       </c>
-      <c r="G157" s="54" t="s">
+      <c r="H157" s="54" t="s">
+        <v>67</v>
+      </c>
+      <c r="I157" s="54" t="s">
+        <v>107</v>
+      </c>
+      <c r="J157" s="54" t="s">
         <v>228</v>
       </c>
-      <c r="H157" s="54" t="s">
-        <v>68</v>
-      </c>
-      <c r="I157" s="54" t="s">
-        <v>108</v>
-      </c>
-      <c r="J157" s="54" t="s">
+      <c r="K157" s="54" t="s">
         <v>229</v>
-      </c>
-      <c r="K157" s="54" t="s">
-        <v>230</v>
       </c>
       <c r="L157" s="54" t="s">
         <v>19</v>
       </c>
       <c r="M157" s="54" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="N157" s="54" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O157" s="54" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P157" s="54" t="s">
         <v>18</v>
       </c>
       <c r="Q157" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="R157" s="54" t="s">
         <v>70</v>
-      </c>
-      <c r="R157" s="54" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="158" spans="2:18" s="6" customFormat="1" ht="36" customHeight="1">
@@ -14843,46 +14844,46 @@
         <v>42</v>
       </c>
       <c r="E161" s="54" t="s">
+        <v>230</v>
+      </c>
+      <c r="F161" s="54" t="s">
+        <v>81</v>
+      </c>
+      <c r="G161" s="54" t="s">
         <v>231</v>
-      </c>
-      <c r="F161" s="54" t="s">
-        <v>82</v>
-      </c>
-      <c r="G161" s="54" t="s">
-        <v>232</v>
       </c>
       <c r="H161" s="54" t="s">
         <v>18</v>
       </c>
       <c r="I161" s="54" t="s">
+        <v>231</v>
+      </c>
+      <c r="J161" s="54" t="s">
         <v>232</v>
       </c>
-      <c r="J161" s="54" t="s">
+      <c r="K161" s="54" t="s">
+        <v>219</v>
+      </c>
+      <c r="L161" s="54" t="s">
+        <v>67</v>
+      </c>
+      <c r="M161" s="54" t="s">
+        <v>107</v>
+      </c>
+      <c r="N161" s="54" t="s">
+        <v>209</v>
+      </c>
+      <c r="O161" s="54" t="s">
         <v>233</v>
-      </c>
-      <c r="K161" s="54" t="s">
-        <v>220</v>
-      </c>
-      <c r="L161" s="54" t="s">
-        <v>68</v>
-      </c>
-      <c r="M161" s="54" t="s">
-        <v>108</v>
-      </c>
-      <c r="N161" s="54" t="s">
-        <v>210</v>
-      </c>
-      <c r="O161" s="54" t="s">
-        <v>234</v>
       </c>
       <c r="P161" s="54" t="s">
         <v>18</v>
       </c>
       <c r="Q161" s="54" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="R161" s="54" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="162" spans="2:18" s="6" customFormat="1" ht="36" customHeight="1">
@@ -14998,49 +14999,49 @@
         <v>41</v>
       </c>
       <c r="D165" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="E165" s="54" t="s">
         <v>70</v>
       </c>
-      <c r="E165" s="54" t="s">
-        <v>71</v>
-      </c>
       <c r="F165" s="54" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G165" s="54" t="s">
+        <v>234</v>
+      </c>
+      <c r="H165" s="54" t="s">
         <v>235</v>
       </c>
-      <c r="H165" s="54" t="s">
+      <c r="I165" s="54" t="s">
+        <v>135</v>
+      </c>
+      <c r="J165" s="54" t="s">
         <v>236</v>
       </c>
-      <c r="I165" s="54" t="s">
-        <v>136</v>
-      </c>
-      <c r="J165" s="54" t="s">
-        <v>237</v>
-      </c>
       <c r="K165" s="54" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L165" s="54" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="M165" s="54" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="N165" s="54" t="s">
         <v>19</v>
       </c>
       <c r="O165" s="54" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="P165" s="54" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q165" s="54" t="s">
         <v>39</v>
       </c>
       <c r="R165" s="54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="166" spans="2:18" s="6" customFormat="1" ht="36" customHeight="1">
@@ -15158,49 +15159,49 @@
       </c>
       <c r="C169" s="6"/>
       <c r="D169" s="54" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E169" s="54" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F169" s="54" t="s">
         <v>42</v>
       </c>
       <c r="G169" s="54" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H169" s="54" t="s">
         <v>18</v>
       </c>
       <c r="I169" s="54" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J169" s="54" t="s">
+        <v>239</v>
+      </c>
+      <c r="K169" s="54" t="s">
+        <v>113</v>
+      </c>
+      <c r="L169" s="54" t="s">
         <v>240</v>
       </c>
-      <c r="K169" s="54" t="s">
-        <v>114</v>
-      </c>
-      <c r="L169" s="54" t="s">
-        <v>241</v>
-      </c>
       <c r="M169" s="54" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N169" s="54" t="s">
         <v>20</v>
       </c>
       <c r="O169" s="54" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="P169" s="54" t="s">
         <v>19</v>
       </c>
       <c r="Q169" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="R169" s="54" t="s">
         <v>67</v>
-      </c>
-      <c r="R169" s="54" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="170" spans="2:18">
@@ -15317,49 +15318,49 @@
       </c>
       <c r="C173" s="6"/>
       <c r="D173" s="54" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E173" s="54" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F173" s="54" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G173" s="54" t="s">
         <v>18</v>
       </c>
       <c r="H173" s="54" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I173" s="54" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J173" s="54" t="s">
+        <v>241</v>
+      </c>
+      <c r="K173" s="54" t="s">
         <v>242</v>
-      </c>
-      <c r="K173" s="54" t="s">
-        <v>243</v>
       </c>
       <c r="L173" s="54" t="s">
         <v>18</v>
       </c>
       <c r="M173" s="54" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N173" s="54" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="O173" s="54" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P173" s="54" t="s">
         <v>19</v>
       </c>
       <c r="Q173" s="54" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="R173" s="54" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="174" spans="2:18">
@@ -15468,34 +15469,34 @@
       </c>
       <c r="C177" s="6"/>
       <c r="D177" s="54" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E177" s="54" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F177" s="54" t="s">
+        <v>58</v>
+      </c>
+      <c r="G177" s="54" t="s">
         <v>59</v>
-      </c>
-      <c r="G177" s="54" t="s">
-        <v>60</v>
       </c>
       <c r="H177" s="54" t="s">
         <v>18</v>
       </c>
       <c r="I177" s="54" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J177" s="54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K177" s="54" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L177" s="54" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M177" s="54" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="N177" s="54" t="s">
         <v>19</v>
@@ -15619,49 +15620,49 @@
       </c>
       <c r="C181" s="6"/>
       <c r="D181" s="54" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E181" s="54" t="s">
+        <v>155</v>
+      </c>
+      <c r="F181" s="54" t="s">
         <v>156</v>
       </c>
-      <c r="F181" s="54" t="s">
+      <c r="G181" s="54" t="s">
+        <v>216</v>
+      </c>
+      <c r="H181" s="54" t="s">
+        <v>246</v>
+      </c>
+      <c r="I181" s="54" t="s">
+        <v>102</v>
+      </c>
+      <c r="J181" s="54" t="s">
         <v>157</v>
       </c>
-      <c r="G181" s="54" t="s">
-        <v>217</v>
-      </c>
-      <c r="H181" s="54" t="s">
-        <v>247</v>
-      </c>
-      <c r="I181" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="J181" s="54" t="s">
-        <v>158</v>
-      </c>
       <c r="K181" s="54" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L181" s="54" t="s">
         <v>18</v>
       </c>
       <c r="M181" s="54" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N181" s="54" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O181" s="54" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P181" s="54" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q181" s="54" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R181" s="54" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="182" spans="2:18">
@@ -15782,49 +15783,49 @@
       </c>
       <c r="C185" s="6"/>
       <c r="D185" s="54" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E185" s="54" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F185" s="54" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G185" s="54" t="s">
         <v>19</v>
       </c>
       <c r="H185" s="54" t="s">
+        <v>66</v>
+      </c>
+      <c r="I185" s="54" t="s">
         <v>67</v>
       </c>
-      <c r="I185" s="54" t="s">
-        <v>68</v>
-      </c>
       <c r="J185" s="54" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K185" s="54" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L185" s="54" t="s">
         <v>18</v>
       </c>
       <c r="M185" s="54" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N185" s="54" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="O185" s="54" t="s">
+        <v>155</v>
+      </c>
+      <c r="P185" s="54" t="s">
         <v>156</v>
-      </c>
-      <c r="P185" s="54" t="s">
-        <v>157</v>
       </c>
       <c r="Q185" s="54" t="s">
         <v>42</v>
       </c>
       <c r="R185" s="54" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="186" spans="2:18">
@@ -15941,49 +15942,49 @@
       </c>
       <c r="C189" s="6"/>
       <c r="D189" s="54" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E189" s="54" t="s">
+        <v>58</v>
+      </c>
+      <c r="F189" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="F189" s="54" t="s">
-        <v>60</v>
-      </c>
       <c r="G189" s="54" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H189" s="54" t="s">
         <v>18</v>
       </c>
       <c r="I189" s="54" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J189" s="54" t="s">
         <v>42</v>
       </c>
       <c r="K189" s="54" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="L189" s="54" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M189" s="54" t="s">
         <v>19</v>
       </c>
       <c r="N189" s="54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="O189" s="54" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P189" s="54" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="Q189" s="54" t="s">
         <v>18</v>
       </c>
       <c r="R189" s="54" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="190" spans="2:18">
@@ -16100,43 +16101,43 @@
       </c>
       <c r="C193" s="6"/>
       <c r="D193" s="54" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E193" s="54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F193" s="54" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G193" s="54" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H193" s="54" t="s">
         <v>18</v>
       </c>
       <c r="I193" s="54" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J193" s="54" t="s">
+        <v>127</v>
+      </c>
+      <c r="K193" s="54" t="s">
         <v>128</v>
       </c>
-      <c r="K193" s="54" t="s">
-        <v>129</v>
-      </c>
       <c r="L193" s="54" t="s">
+        <v>252</v>
+      </c>
+      <c r="M193" s="54" t="s">
         <v>253</v>
       </c>
-      <c r="M193" s="54" t="s">
-        <v>254</v>
-      </c>
       <c r="N193" s="54" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O193" s="54" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P193" s="54" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q193" s="54" t="s">
         <v>20</v>
@@ -16263,49 +16264,49 @@
       </c>
       <c r="C197" s="6"/>
       <c r="D197" s="54" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E197" s="54" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F197" s="54" t="s">
         <v>41</v>
       </c>
       <c r="G197" s="54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H197" s="54" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I197" s="54" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J197" s="54" t="s">
         <v>40</v>
       </c>
       <c r="K197" s="54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="L197" s="54" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="M197" s="54" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N197" s="54" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="O197" s="54" t="s">
         <v>40</v>
       </c>
       <c r="P197" s="54" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q197" s="54" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="R197" s="54" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="198" spans="2:18">
@@ -16429,46 +16430,46 @@
         <v>18</v>
       </c>
       <c r="E201" s="54" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F201" s="54" t="s">
         <v>42</v>
       </c>
       <c r="G201" s="54" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H201" s="54" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I201" s="54" t="s">
+        <v>257</v>
+      </c>
+      <c r="J201" s="54" t="s">
+        <v>78</v>
+      </c>
+      <c r="K201" s="54" t="s">
+        <v>117</v>
+      </c>
+      <c r="L201" s="54" t="s">
+        <v>126</v>
+      </c>
+      <c r="M201" s="54" t="s">
+        <v>222</v>
+      </c>
+      <c r="N201" s="54" t="s">
         <v>258</v>
-      </c>
-      <c r="J201" s="54" t="s">
-        <v>79</v>
-      </c>
-      <c r="K201" s="54" t="s">
-        <v>118</v>
-      </c>
-      <c r="L201" s="54" t="s">
-        <v>127</v>
-      </c>
-      <c r="M201" s="54" t="s">
-        <v>223</v>
-      </c>
-      <c r="N201" s="54" t="s">
-        <v>259</v>
       </c>
       <c r="O201" s="54" t="s">
         <v>38</v>
       </c>
       <c r="P201" s="54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="Q201" s="54" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="R201" s="54" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="202" spans="2:18">
@@ -16582,34 +16583,34 @@
         <v>19</v>
       </c>
       <c r="E205" s="54" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F205" s="54" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G205" s="54" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H205" s="54" t="s">
         <v>18</v>
       </c>
       <c r="I205" s="54" t="s">
+        <v>259</v>
+      </c>
+      <c r="J205" s="54" t="s">
         <v>260</v>
-      </c>
-      <c r="J205" s="54" t="s">
-        <v>261</v>
       </c>
       <c r="K205" s="54" t="s">
         <v>42</v>
       </c>
       <c r="L205" s="54" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M205" s="54" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="N205" s="54" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O205" s="54" t="s">
         <v>19</v>
@@ -16690,7 +16691,9 @@
       <c r="F208" s="55" t="s">
         <v>859</v>
       </c>
-      <c r="G208" s="55"/>
+      <c r="G208" s="55" t="s">
+        <v>351</v>
+      </c>
       <c r="H208" s="55" t="s">
         <v>886</v>
       </c>
@@ -16732,49 +16735,49 @@
       </c>
       <c r="C209" s="6"/>
       <c r="D209" s="54" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E209" s="54" t="s">
+        <v>261</v>
+      </c>
+      <c r="F209" s="54" t="s">
         <v>262</v>
       </c>
-      <c r="F209" s="54" t="s">
+      <c r="G209" s="54" t="s">
         <v>263</v>
       </c>
-      <c r="G209" s="54" t="s">
-        <v>264</v>
-      </c>
       <c r="H209" s="54" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I209" s="54" t="s">
         <v>42</v>
       </c>
       <c r="J209" s="54" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K209" s="54" t="s">
+        <v>264</v>
+      </c>
+      <c r="L209" s="54" t="s">
         <v>265</v>
       </c>
-      <c r="L209" s="54" t="s">
+      <c r="M209" s="54" t="s">
         <v>266</v>
       </c>
-      <c r="M209" s="54" t="s">
+      <c r="N209" s="54" t="s">
         <v>267</v>
       </c>
-      <c r="N209" s="54" t="s">
+      <c r="O209" s="54" t="s">
+        <v>126</v>
+      </c>
+      <c r="P209" s="54" t="s">
         <v>268</v>
       </c>
-      <c r="O209" s="54" t="s">
-        <v>127</v>
-      </c>
-      <c r="P209" s="54" t="s">
+      <c r="Q209" s="54" t="s">
         <v>269</v>
       </c>
-      <c r="Q209" s="54" t="s">
-        <v>270</v>
-      </c>
       <c r="R209" s="54" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="210" spans="2:18">
@@ -16789,7 +16792,9 @@
       <c r="F210" s="56" t="s">
         <v>860</v>
       </c>
-      <c r="G210" s="56"/>
+      <c r="G210" s="56" t="s">
+        <v>352</v>
+      </c>
       <c r="H210" s="56" t="s">
         <v>887</v>
       </c>
@@ -16893,49 +16898,49 @@
       </c>
       <c r="C213" s="6"/>
       <c r="D213" s="54" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E213" s="54" t="s">
         <v>18</v>
       </c>
       <c r="F213" s="54" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G213" s="54" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H213" s="54" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I213" s="54" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J213" s="54" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K213" s="54" t="s">
+        <v>271</v>
+      </c>
+      <c r="L213" s="54" t="s">
+        <v>117</v>
+      </c>
+      <c r="M213" s="54" t="s">
         <v>272</v>
       </c>
-      <c r="L213" s="54" t="s">
-        <v>118</v>
-      </c>
-      <c r="M213" s="54" t="s">
-        <v>273</v>
-      </c>
       <c r="N213" s="54" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="O213" s="54" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P213" s="54" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q213" s="54" t="s">
         <v>18</v>
       </c>
       <c r="R213" s="54" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="214" spans="2:18">
@@ -17052,49 +17057,49 @@
       </c>
       <c r="C217" s="6"/>
       <c r="D217" s="54" t="s">
+        <v>273</v>
+      </c>
+      <c r="E217" s="54" t="s">
         <v>274</v>
       </c>
-      <c r="E217" s="54" t="s">
-        <v>275</v>
-      </c>
       <c r="F217" s="54" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G217" s="54" t="s">
+        <v>214</v>
+      </c>
+      <c r="H217" s="54" t="s">
         <v>215</v>
-      </c>
-      <c r="H217" s="54" t="s">
-        <v>216</v>
       </c>
       <c r="I217" s="54" t="s">
         <v>18</v>
       </c>
       <c r="J217" s="54" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="K217" s="54" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="L217" s="54" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M217" s="54" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N217" s="54" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O217" s="54" t="s">
         <v>18</v>
       </c>
       <c r="P217" s="54" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q217" s="54" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="R217" s="54" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="218" spans="2:18">
@@ -17211,46 +17216,46 @@
       </c>
       <c r="C221" s="6"/>
       <c r="D221" s="54" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E221" s="54" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F221" s="54" t="s">
         <v>19</v>
       </c>
       <c r="G221" s="54" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H221" s="54" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I221" s="54" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J221" s="54" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K221" s="54" t="s">
         <v>20</v>
       </c>
       <c r="L221" s="54" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="M221" s="54" t="s">
         <v>18</v>
       </c>
       <c r="N221" s="54" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="O221" s="54" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="P221" s="54" t="s">
         <v>20</v>
       </c>
       <c r="Q221" s="54" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="R221" s="54" t="s">
         <v>19</v>
@@ -17372,49 +17377,49 @@
       </c>
       <c r="C225" s="6"/>
       <c r="D225" s="54" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E225" s="54" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F225" s="54" t="s">
         <v>42</v>
       </c>
       <c r="G225" s="54" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H225" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="I225" s="54" t="s">
         <v>76</v>
       </c>
-      <c r="I225" s="54" t="s">
-        <v>77</v>
-      </c>
       <c r="J225" s="54" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K225" s="54" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L225" s="54" t="s">
         <v>18</v>
       </c>
       <c r="M225" s="54" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N225" s="54" t="s">
+        <v>280</v>
+      </c>
+      <c r="O225" s="54" t="s">
+        <v>75</v>
+      </c>
+      <c r="P225" s="54" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q225" s="54" t="s">
+        <v>107</v>
+      </c>
+      <c r="R225" s="54" t="s">
         <v>281</v>
-      </c>
-      <c r="O225" s="54" t="s">
-        <v>76</v>
-      </c>
-      <c r="P225" s="54" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q225" s="54" t="s">
-        <v>108</v>
-      </c>
-      <c r="R225" s="54" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="226" spans="2:18">
@@ -17536,46 +17541,46 @@
         <v>19</v>
       </c>
       <c r="E229" s="54" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F229" s="54" t="s">
+        <v>112</v>
+      </c>
+      <c r="G229" s="54" t="s">
+        <v>248</v>
+      </c>
+      <c r="H229" s="54" t="s">
         <v>113</v>
       </c>
-      <c r="G229" s="54" t="s">
-        <v>249</v>
-      </c>
-      <c r="H229" s="54" t="s">
-        <v>114</v>
-      </c>
       <c r="I229" s="54" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J229" s="54" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K229" s="54" t="s">
         <v>18</v>
       </c>
       <c r="L229" s="54" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M229" s="54" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N229" s="54" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O229" s="54" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P229" s="54" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q229" s="54" t="s">
         <v>19</v>
       </c>
       <c r="R229" s="54" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="230" spans="2:18">
@@ -17680,28 +17685,28 @@
       </c>
       <c r="C233" s="6"/>
       <c r="D233" s="54" t="s">
+        <v>58</v>
+      </c>
+      <c r="E233" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="E233" s="54" t="s">
-        <v>60</v>
-      </c>
       <c r="F233" s="54" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G233" s="54" t="s">
         <v>18</v>
       </c>
       <c r="H233" s="54" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I233" s="54" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="J233" s="54" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K233" s="54" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L233" s="54" t="s">
         <v>39</v>
